--- a/Excel/LanguageData.xlsx
+++ b/Excel/LanguageData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\iot-server-gitlab\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\iot-server\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40ADA021-3604-4AEF-88DF-56529BE0C51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15960" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15960" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="LALALA" sheetId="1" r:id="rId1"/>
@@ -19,12 +18,12 @@
     <definedName name="NamedRange7">#REF!</definedName>
     <definedName name="WMW">LALALA!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -64,21 +63,12 @@
     <t>轉發目標</t>
   </si>
   <si>
-    <t>Forward Target</t>
-  </si>
-  <si>
     <t>網絡狀態</t>
   </si>
   <si>
-    <t>Network State</t>
-  </si>
-  <si>
     <t>Mask</t>
   </si>
   <si>
-    <t>掩碼</t>
-  </si>
-  <si>
     <t>NetProtocol</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,13 +173,80 @@
   </si>
   <si>
     <t>Enter Local Port</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Connecting</t>
+  </si>
+  <si>
+    <t>Connecting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>連接中</t>
+  </si>
+  <si>
+    <t>NotConnecting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未連接</t>
+  </si>
+  <si>
+    <t>Not Connecting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遮罩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>State</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>original data</t>
+  </si>
+  <si>
+    <t>OriginalData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原始資料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot 10</t>
+  </si>
+  <si>
+    <t>機器人-十進制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot 16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>機器人-十六進制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Robot16</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -325,7 +382,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="1" xr:uid="{4508D25C-63AD-4003-84C8-D91FD1C9E385}"/>
+    <cellStyle name="一般 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -537,17 +594,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W364"/>
-  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.69921875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.8984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="111.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="14.3984375" style="6"/>
+    <col min="1" max="1" width="42.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="111.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="14.42578125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -558,7 +615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
@@ -569,20 +626,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>8</v>
@@ -591,9 +648,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>10</v>
@@ -602,163 +659,193 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
-        <v>15</v>
-      </c>
       <c r="B8" s="15" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="C10" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+      <c r="B15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="7" t="s">
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="4" t="s">
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="4"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="7"/>
-    </row>
-    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="7"/>
-    </row>
-    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="4"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="4"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="7"/>
-    </row>
-    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="2"/>
       <c r="C22" s="7"/>
     </row>
-    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="2"/>
       <c r="C23" s="7"/>
     </row>
-    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="2"/>
       <c r="C24" s="7"/>
@@ -783,7 +870,7 @@
       <c r="V24" s="2"/>
       <c r="W24" s="2"/>
     </row>
-    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="2"/>
       <c r="C25" s="7"/>
@@ -808,1367 +895,1367 @@
       <c r="V25" s="2"/>
       <c r="W25" s="2"/>
     </row>
-    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
       <c r="C26" s="7"/>
     </row>
-    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="1"/>
       <c r="C27" s="7"/>
     </row>
-    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="7"/>
     </row>
-    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="7"/>
     </row>
-    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="7"/>
     </row>
-    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="1"/>
       <c r="C31" s="7"/>
     </row>
-    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="1"/>
       <c r="C32" s="7"/>
     </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="1"/>
       <c r="C33" s="7"/>
     </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="1"/>
       <c r="C34" s="7"/>
     </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="1"/>
       <c r="C35" s="7"/>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="1"/>
       <c r="C36" s="7"/>
     </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="1"/>
       <c r="C37" s="7"/>
     </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="1"/>
       <c r="C38" s="7"/>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="1"/>
       <c r="C39" s="7"/>
     </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="7"/>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="1"/>
       <c r="C41" s="7"/>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="1"/>
       <c r="C42" s="7"/>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="1"/>
       <c r="C43" s="7"/>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="1"/>
       <c r="C44" s="7"/>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="1"/>
       <c r="C45" s="7"/>
     </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="1"/>
       <c r="C46" s="7"/>
     </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="1"/>
       <c r="C47" s="7"/>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="1"/>
       <c r="C48" s="7"/>
     </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="1"/>
       <c r="C49" s="7"/>
     </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="1"/>
       <c r="C50" s="7"/>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="1"/>
       <c r="C51" s="7"/>
     </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="1"/>
       <c r="C52" s="7"/>
     </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="1"/>
       <c r="C53" s="7"/>
     </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="1"/>
       <c r="C54" s="7"/>
     </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="1"/>
       <c r="C55" s="7"/>
     </row>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="1"/>
       <c r="C56" s="7"/>
     </row>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="1"/>
       <c r="C57" s="7"/>
     </row>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="1"/>
       <c r="C58" s="7"/>
     </row>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="1"/>
       <c r="C59" s="7"/>
     </row>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="1"/>
       <c r="C60" s="7"/>
     </row>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="1"/>
       <c r="C61" s="7"/>
     </row>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="1"/>
       <c r="C62" s="7"/>
     </row>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="1"/>
       <c r="C63" s="7"/>
     </row>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="1"/>
       <c r="C64" s="7"/>
     </row>
-    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="1"/>
       <c r="C65" s="7"/>
     </row>
-    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="1"/>
       <c r="C66" s="7"/>
     </row>
-    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="1"/>
       <c r="C67" s="7"/>
     </row>
-    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="1"/>
       <c r="C68" s="7"/>
     </row>
-    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="1"/>
       <c r="C69" s="7"/>
     </row>
-    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="1"/>
       <c r="C70" s="7"/>
     </row>
-    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="1"/>
       <c r="C71" s="7"/>
     </row>
-    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="1"/>
       <c r="C72" s="7"/>
     </row>
-    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="1"/>
       <c r="C73" s="7"/>
     </row>
-    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="1"/>
       <c r="C74" s="7"/>
     </row>
-    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="1"/>
       <c r="C75" s="7"/>
     </row>
-    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="1"/>
       <c r="C76" s="7"/>
     </row>
-    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="1"/>
       <c r="C77" s="7"/>
     </row>
-    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="1"/>
       <c r="C78" s="7"/>
     </row>
-    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
     </row>
-    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="C81" s="1"/>
     </row>
-    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="1"/>
       <c r="C83" s="7"/>
     </row>
-    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="1"/>
       <c r="C85" s="7"/>
     </row>
-    <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="1"/>
       <c r="C86" s="7"/>
     </row>
-    <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="2"/>
       <c r="C87" s="7"/>
     </row>
-    <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4"/>
       <c r="B88" s="2"/>
       <c r="C88" s="7"/>
     </row>
-    <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4"/>
       <c r="B89" s="2"/>
       <c r="C89" s="7"/>
     </row>
-    <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="2"/>
       <c r="C90" s="7"/>
     </row>
-    <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4"/>
       <c r="B91" s="2"/>
       <c r="C91" s="7"/>
     </row>
-    <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4"/>
       <c r="B92" s="2"/>
       <c r="C92" s="7"/>
     </row>
-    <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4"/>
       <c r="B93" s="2"/>
       <c r="C93" s="7"/>
     </row>
-    <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4"/>
       <c r="B94" s="2"/>
       <c r="C94" s="7"/>
     </row>
-    <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4"/>
       <c r="B95" s="2"/>
       <c r="C95" s="7"/>
     </row>
-    <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="B96" s="1"/>
       <c r="C96" s="7"/>
     </row>
-    <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="B97" s="1"/>
       <c r="C97" s="7"/>
     </row>
-    <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="1"/>
       <c r="C98" s="7"/>
     </row>
-    <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="1"/>
       <c r="C99" s="7"/>
     </row>
-    <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="1"/>
       <c r="C100" s="7"/>
     </row>
-    <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="1"/>
       <c r="C101" s="7"/>
     </row>
-    <row r="102" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="B102" s="1"/>
       <c r="C102" s="7"/>
     </row>
-    <row r="103" spans="1:3" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:3" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="1"/>
       <c r="C103" s="7"/>
     </row>
-    <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="1"/>
       <c r="C104" s="7"/>
     </row>
-    <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="1"/>
       <c r="C105" s="7"/>
     </row>
-    <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="B106" s="1"/>
       <c r="C106" s="7"/>
     </row>
-    <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="B107" s="1"/>
       <c r="C107" s="7"/>
     </row>
-    <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="1"/>
       <c r="C108" s="7"/>
     </row>
-    <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="1"/>
       <c r="C109" s="7"/>
     </row>
-    <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="B110" s="1"/>
       <c r="C110" s="7"/>
     </row>
-    <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="1"/>
       <c r="C111" s="7"/>
     </row>
-    <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="B112" s="1"/>
       <c r="C112" s="7"/>
     </row>
-    <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="B113" s="1"/>
       <c r="C113" s="7"/>
     </row>
-    <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="1"/>
       <c r="C114" s="7"/>
     </row>
-    <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3"/>
       <c r="B115" s="1"/>
       <c r="C115" s="7"/>
     </row>
-    <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3"/>
       <c r="B116" s="1"/>
       <c r="C116" s="7"/>
     </row>
-    <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3"/>
       <c r="B117" s="1"/>
       <c r="C117" s="7"/>
     </row>
-    <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3"/>
       <c r="B118" s="1"/>
       <c r="C118" s="7"/>
     </row>
-    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3"/>
       <c r="B119" s="1"/>
       <c r="C119" s="7"/>
     </row>
-    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3"/>
       <c r="B120" s="1"/>
       <c r="C120" s="7"/>
     </row>
-    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3"/>
       <c r="B121" s="1"/>
       <c r="C121" s="7"/>
     </row>
-    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3"/>
       <c r="B122" s="1"/>
       <c r="C122" s="7"/>
     </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3"/>
       <c r="B123" s="1"/>
       <c r="C123" s="7"/>
     </row>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3"/>
       <c r="B124" s="1"/>
       <c r="C124" s="7"/>
     </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3"/>
       <c r="B125" s="1"/>
       <c r="C125" s="7"/>
     </row>
-    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
     </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
     </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
     </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
     </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
     </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
     </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
     </row>
-    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
     </row>
-    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
     </row>
-    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
     </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
     </row>
-    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
     </row>
-    <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
     </row>
-    <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
     </row>
-    <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
     </row>
-    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
     </row>
-    <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
     </row>
-    <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
     </row>
-    <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
     </row>
-    <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
     </row>
-    <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
     </row>
-    <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
     </row>
-    <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
     </row>
-    <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
     </row>
-    <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
     </row>
-    <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
     </row>
-    <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
     </row>
-    <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
     </row>
-    <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
     </row>
-    <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
     </row>
-    <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
     </row>
-    <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
     </row>
-    <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
     </row>
-    <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
       <c r="B171" s="7"/>
     </row>
-    <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
       <c r="B172" s="7"/>
     </row>
-    <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
       <c r="B173" s="7"/>
     </row>
-    <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
       <c r="B174" s="7"/>
     </row>
-    <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
       <c r="B175" s="7"/>
     </row>
-    <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
       <c r="B176" s="7"/>
     </row>
-    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
       <c r="B177" s="7"/>
     </row>
-    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
       <c r="B178" s="7"/>
     </row>
-    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
       <c r="B179" s="7"/>
     </row>
-    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
       <c r="B180" s="7"/>
     </row>
-    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
       <c r="B181" s="7"/>
     </row>
-    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
       <c r="B182" s="7"/>
     </row>
-    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
       <c r="B183" s="7"/>
     </row>
-    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
       <c r="B184" s="7"/>
     </row>
-    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
       <c r="B185" s="7"/>
     </row>
-    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
       <c r="B186" s="7"/>
     </row>
-    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
       <c r="B187" s="7"/>
     </row>
-    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
       <c r="B188" s="7"/>
     </row>
-    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
       <c r="B189" s="7"/>
     </row>
-    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
       <c r="B190" s="7"/>
       <c r="C190" s="8"/>
     </row>
-    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
       <c r="B191" s="7"/>
     </row>
-    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
       <c r="B192" s="7"/>
     </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
       <c r="B193" s="7"/>
     </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
     </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
     </row>
-    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
       <c r="B196" s="7"/>
     </row>
-    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
       <c r="B197" s="7"/>
     </row>
-    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
       <c r="B198" s="7"/>
     </row>
-    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="B199" s="1"/>
       <c r="C199" s="9"/>
     </row>
-    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="B200" s="1"/>
       <c r="C200" s="9"/>
     </row>
-    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="3"/>
       <c r="B201" s="1"/>
       <c r="C201" s="9"/>
     </row>
-    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="3"/>
       <c r="B202" s="1"/>
       <c r="C202" s="9"/>
     </row>
-    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
       <c r="B203" s="1"/>
       <c r="C203" s="9"/>
     </row>
-    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="3"/>
       <c r="B204" s="1"/>
       <c r="C204" s="7"/>
     </row>
-    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="3"/>
       <c r="B205" s="1"/>
       <c r="C205" s="7"/>
     </row>
-    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="3"/>
       <c r="B206" s="1"/>
       <c r="C206" s="7"/>
     </row>
-    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
       <c r="B207" s="1"/>
       <c r="C207" s="7"/>
     </row>
-    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="3"/>
       <c r="B208" s="1"/>
       <c r="C208" s="7"/>
     </row>
-    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="3"/>
       <c r="B209" s="1"/>
       <c r="C209" s="7"/>
     </row>
-    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="B210" s="1"/>
       <c r="C210" s="7"/>
     </row>
-    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
       <c r="B211" s="1"/>
       <c r="C211" s="7"/>
     </row>
-    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
       <c r="B212" s="1"/>
       <c r="C212" s="7"/>
     </row>
-    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
       <c r="B213" s="1"/>
       <c r="C213" s="7"/>
     </row>
-    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
       <c r="B214" s="1"/>
       <c r="C214" s="7"/>
     </row>
-    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
       <c r="B215" s="1"/>
       <c r="C215" s="7"/>
     </row>
-    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="3"/>
       <c r="B216" s="1"/>
       <c r="C216" s="7"/>
     </row>
-    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
       <c r="B217" s="1"/>
       <c r="C217" s="7"/>
     </row>
-    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
       <c r="B218" s="1"/>
       <c r="C218" s="7"/>
     </row>
-    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="3"/>
       <c r="B219" s="1"/>
       <c r="C219" s="7"/>
     </row>
-    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
       <c r="B220" s="1"/>
       <c r="C220" s="7"/>
     </row>
-    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
       <c r="B221" s="1"/>
       <c r="C221" s="7"/>
     </row>
-    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
       <c r="B222" s="1"/>
       <c r="C222" s="7"/>
     </row>
-    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
       <c r="B223" s="1"/>
       <c r="C223" s="7"/>
     </row>
-    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
       <c r="B224" s="1"/>
       <c r="C224" s="7"/>
     </row>
-    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
       <c r="B225" s="1"/>
       <c r="C225" s="7"/>
     </row>
-    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
       <c r="B226" s="1"/>
       <c r="C226" s="7"/>
     </row>
-    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
       <c r="B227" s="1"/>
       <c r="C227" s="7"/>
     </row>
-    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
       <c r="B228" s="1"/>
       <c r="C228" s="7"/>
     </row>
-    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="3"/>
       <c r="B229" s="1"/>
       <c r="C229" s="7"/>
     </row>
-    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="3"/>
       <c r="B230" s="1"/>
       <c r="C230" s="7"/>
     </row>
-    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="3"/>
       <c r="B231" s="1"/>
       <c r="C231" s="7"/>
     </row>
-    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="3"/>
       <c r="B232" s="1"/>
       <c r="C232" s="7"/>
     </row>
-    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="3"/>
       <c r="B233" s="1"/>
       <c r="C233" s="7"/>
     </row>
-    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="3"/>
       <c r="B234" s="1"/>
       <c r="C234" s="7"/>
     </row>
-    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="3"/>
       <c r="B235" s="1"/>
       <c r="C235" s="7"/>
     </row>
-    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="3"/>
       <c r="B236" s="1"/>
       <c r="C236" s="7"/>
     </row>
-    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="3"/>
       <c r="B237" s="1"/>
       <c r="C237" s="7"/>
     </row>
-    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="3"/>
       <c r="B238" s="1"/>
       <c r="C238" s="7"/>
     </row>
-    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="3"/>
       <c r="B239" s="1"/>
       <c r="C239" s="7"/>
     </row>
-    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="3"/>
       <c r="B240" s="1"/>
       <c r="C240" s="7"/>
     </row>
-    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="3"/>
       <c r="B241" s="1"/>
       <c r="C241" s="7"/>
     </row>
-    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="3"/>
       <c r="B242" s="1"/>
       <c r="C242" s="7"/>
     </row>
-    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="3"/>
       <c r="B243" s="1"/>
       <c r="C243" s="7"/>
     </row>
-    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="3"/>
       <c r="B244" s="1"/>
       <c r="C244" s="7"/>
     </row>
-    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="3"/>
       <c r="B245" s="1"/>
       <c r="C245" s="7"/>
     </row>
-    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="3"/>
       <c r="B246" s="1"/>
       <c r="C246" s="7"/>
     </row>
-    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="3"/>
       <c r="B247" s="1"/>
       <c r="C247" s="7"/>
     </row>
-    <row r="248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="3"/>
       <c r="B248" s="1"/>
       <c r="C248" s="7"/>
     </row>
-    <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="3"/>
       <c r="B249" s="1"/>
       <c r="C249" s="7"/>
     </row>
-    <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="3"/>
       <c r="B250" s="1"/>
       <c r="C250" s="7"/>
     </row>
-    <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="3"/>
       <c r="B251" s="1"/>
       <c r="C251" s="7"/>
     </row>
-    <row r="252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="3"/>
       <c r="B252" s="1"/>
       <c r="C252" s="7"/>
     </row>
-    <row r="253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="3"/>
       <c r="B253" s="1"/>
     </row>
-    <row r="254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="3"/>
       <c r="B254" s="1"/>
     </row>
-    <row r="255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="3"/>
       <c r="B255" s="1"/>
       <c r="C255" s="7"/>
     </row>
-    <row r="256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="3"/>
       <c r="B256" s="1"/>
       <c r="C256" s="7"/>
     </row>
-    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="3"/>
       <c r="B257" s="1"/>
       <c r="C257" s="7"/>
     </row>
-    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="3"/>
       <c r="B258" s="1"/>
       <c r="C258" s="7"/>
     </row>
-    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="3"/>
       <c r="B259" s="1"/>
       <c r="C259" s="7"/>
     </row>
-    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="3"/>
       <c r="B260" s="1"/>
       <c r="C260" s="7"/>
     </row>
-    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="3"/>
       <c r="B261" s="1"/>
       <c r="C261" s="7"/>
     </row>
-    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="3"/>
       <c r="B262" s="1"/>
       <c r="C262" s="7"/>
     </row>
-    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="3"/>
       <c r="B263" s="1"/>
       <c r="C263" s="7"/>
     </row>
-    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="3"/>
       <c r="B264" s="1"/>
       <c r="C264" s="7"/>
     </row>
-    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="3"/>
       <c r="B265" s="1"/>
       <c r="C265" s="7"/>
     </row>
-    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="3"/>
       <c r="B266" s="1"/>
       <c r="C266" s="7"/>
     </row>
-    <row r="267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="3"/>
       <c r="B267" s="1"/>
     </row>
-    <row r="268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="3"/>
       <c r="B268" s="1"/>
     </row>
-    <row r="269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="3"/>
       <c r="B269" s="1"/>
     </row>
-    <row r="270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="3"/>
       <c r="B270" s="1"/>
     </row>
-    <row r="271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="3"/>
       <c r="B271" s="1"/>
     </row>
-    <row r="272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="3"/>
       <c r="B272" s="1"/>
     </row>
-    <row r="273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="3"/>
       <c r="B273" s="1"/>
       <c r="C273" s="10"/>
     </row>
-    <row r="274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="3"/>
       <c r="B274" s="1"/>
       <c r="C274" s="10"/>
     </row>
-    <row r="275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="3"/>
       <c r="B275" s="1"/>
       <c r="C275" s="10"/>
     </row>
-    <row r="276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5"/>
       <c r="B276" s="1"/>
       <c r="C276" s="10"/>
     </row>
-    <row r="277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5"/>
       <c r="B277" s="1"/>
       <c r="C277" s="10"/>
     </row>
-    <row r="278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="5"/>
       <c r="B278" s="1"/>
       <c r="C278" s="10"/>
     </row>
-    <row r="279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5"/>
       <c r="B279" s="1"/>
       <c r="C279" s="10"/>
     </row>
-    <row r="280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5"/>
       <c r="B280" s="1"/>
       <c r="C280" s="10"/>
     </row>
-    <row r="281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5"/>
       <c r="B281" s="1"/>
       <c r="C281" s="10"/>
     </row>
-    <row r="282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5"/>
       <c r="B282" s="1"/>
       <c r="C282" s="10"/>
     </row>
-    <row r="283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5"/>
       <c r="B283" s="1"/>
       <c r="C283" s="10"/>
     </row>
-    <row r="284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5"/>
       <c r="B284" s="1"/>
       <c r="C284" s="10"/>
     </row>
-    <row r="285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5"/>
       <c r="B285" s="1"/>
       <c r="C285" s="10"/>
     </row>
-    <row r="286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5"/>
       <c r="B286" s="1"/>
       <c r="C286" s="10"/>
     </row>
-    <row r="287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="5"/>
       <c r="B287" s="1"/>
       <c r="C287" s="10"/>
     </row>
-    <row r="288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5"/>
       <c r="B288" s="1"/>
       <c r="C288" s="10"/>
     </row>
-    <row r="289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5"/>
       <c r="B289" s="1"/>
       <c r="C289" s="10"/>
     </row>
-    <row r="290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5"/>
       <c r="B290" s="1"/>
       <c r="C290" s="10"/>
     </row>
-    <row r="291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5"/>
       <c r="C291" s="10"/>
     </row>
-    <row r="292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5"/>
       <c r="C292" s="10"/>
     </row>
-    <row r="293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5"/>
       <c r="B293" s="1"/>
       <c r="C293" s="10"/>
     </row>
-    <row r="294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="5"/>
       <c r="B294" s="1"/>
       <c r="C294" s="10"/>
     </row>
-    <row r="295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="5"/>
       <c r="B295" s="1"/>
       <c r="C295" s="10"/>
     </row>
-    <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="5"/>
       <c r="B296" s="1"/>
       <c r="C296" s="10"/>
     </row>
-    <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="5"/>
       <c r="B297" s="1"/>
     </row>
-    <row r="298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="5"/>
       <c r="B298" s="1"/>
     </row>
-    <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="5"/>
       <c r="B299" s="1"/>
     </row>
-    <row r="300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="5"/>
       <c r="B300" s="1"/>
     </row>
-    <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="5"/>
       <c r="B301" s="1"/>
     </row>
-    <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5"/>
       <c r="B302" s="1"/>
     </row>
-    <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5"/>
       <c r="B303" s="1"/>
     </row>
-    <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5"/>
       <c r="B304" s="1"/>
     </row>
-    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5"/>
     </row>
-    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5"/>
       <c r="B306" s="1"/>
     </row>
-    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5"/>
       <c r="B307" s="1"/>
     </row>
-    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="5"/>
       <c r="B308" s="1"/>
     </row>
-    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5"/>
       <c r="B309" s="1"/>
     </row>
-    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5"/>
       <c r="B310" s="1"/>
     </row>
-    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="5"/>
       <c r="B311" s="1"/>
     </row>
-    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="5"/>
       <c r="B312" s="1"/>
     </row>
-    <row r="364" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C364" s="6" t="s">
         <v>2</v>
       </c>

--- a/Excel/LanguageData.xlsx
+++ b/Excel/LanguageData.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\iot-server\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\iot-server\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E53E0D0-726D-4A93-B8F7-4402C706E849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15960" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LALALA" sheetId="1" r:id="rId1"/>
@@ -18,236 +19,652 @@
     <definedName name="NamedRange7">#REF!</definedName>
     <definedName name="WMW">LALALA!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="178">
   <si>
     <t>ID</t>
   </si>
   <si>
     <t>zh-TW,繁體中文</t>
+  </si>
+  <si>
+    <t>en-US,English</t>
+  </si>
+  <si>
+    <t>ja-JP,日本語</t>
+  </si>
+  <si>
+    <t>de-DE,Deutsch</t>
+  </si>
+  <si>
+    <t>fr-FR,Français</t>
+  </si>
+  <si>
+    <t>es-ES,Español</t>
+  </si>
+  <si>
+    <t>pt-BR,Português</t>
+  </si>
+  <si>
+    <t>vi-VN,Tiếng Việt</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>名稱</t>
+  </si>
+  <si>
+    <t>名前</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Nome</t>
+  </si>
+  <si>
+    <t>Tên</t>
+  </si>
+  <si>
+    <t>NetProtocol</t>
+  </si>
+  <si>
+    <t>網絡協議</t>
+  </si>
+  <si>
+    <t>Network Protocol</t>
+  </si>
+  <si>
+    <t>ネットワークプロトコル</t>
+  </si>
+  <si>
+    <t>Netzwerkprotokoll</t>
+  </si>
+  <si>
+    <t>Protocole réseau</t>
+  </si>
+  <si>
+    <t>Protocolo de red</t>
+  </si>
+  <si>
+    <t>Protocolo de rede</t>
+  </si>
+  <si>
+    <t>Giao thức mạng</t>
+  </si>
+  <si>
+    <t>RemotePort</t>
+  </si>
+  <si>
+    <t>遠端端口</t>
+  </si>
+  <si>
+    <t>Remote Port</t>
+  </si>
+  <si>
+    <t>リモートポート</t>
+  </si>
+  <si>
+    <t>Remote-Port</t>
+  </si>
+  <si>
+    <t>Port distant</t>
+  </si>
+  <si>
+    <t>Puerto remoto</t>
+  </si>
+  <si>
+    <t>Porta remota</t>
+  </si>
+  <si>
+    <t>Cổng từ xa</t>
+  </si>
+  <si>
+    <t>LocalPort</t>
+  </si>
+  <si>
+    <t>本地端口</t>
+  </si>
+  <si>
+    <t>Local Port</t>
+  </si>
+  <si>
+    <t>ローカルポート</t>
+  </si>
+  <si>
+    <t>Lokaler Port</t>
+  </si>
+  <si>
+    <t>Port local</t>
+  </si>
+  <si>
+    <t>Puerto local</t>
+  </si>
+  <si>
+    <t>Porta local</t>
+  </si>
+  <si>
+    <t>Cổng cục bộ</t>
+  </si>
+  <si>
+    <t>ForwardTarget</t>
+  </si>
+  <si>
+    <t>轉發目標</t>
+  </si>
+  <si>
+    <t>Forward Target</t>
+  </si>
+  <si>
+    <t>転送先</t>
+  </si>
+  <si>
+    <t>Weiterleitungsziel</t>
+  </si>
+  <si>
+    <t>Cible de transfert</t>
+  </si>
+  <si>
+    <t>Destino de reenvío</t>
+  </si>
+  <si>
+    <t>Destino de encaminhamento</t>
+  </si>
+  <si>
+    <t>Mục tiêu chuyển tiếp</t>
+  </si>
+  <si>
+    <t>NetState</t>
+  </si>
+  <si>
+    <t>網絡狀態</t>
+  </si>
+  <si>
+    <t>Network State</t>
+  </si>
+  <si>
+    <t>ネットワーク状態</t>
+  </si>
+  <si>
+    <t>Netzwerkstatus</t>
+  </si>
+  <si>
+    <t>État du réseau</t>
+  </si>
+  <si>
+    <t>Estado de red</t>
+  </si>
+  <si>
+    <t>Estado da rede</t>
+  </si>
+  <si>
+    <t>Trạng thái mạng</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>遮罩</t>
+  </si>
+  <si>
+    <t>マスク</t>
+  </si>
+  <si>
+    <t>Maske</t>
+  </si>
+  <si>
+    <t>Masque</t>
+  </si>
+  <si>
+    <t>Máscara</t>
+  </si>
+  <si>
+    <t>Mặt nạ</t>
+  </si>
+  <si>
+    <t>Exit</t>
+  </si>
+  <si>
+    <t>退出</t>
+  </si>
+  <si>
+    <t>終了</t>
+  </si>
+  <si>
+    <t>Beenden</t>
+  </si>
+  <si>
+    <t>Quitter</t>
+  </si>
+  <si>
+    <t>Salir</t>
+  </si>
+  <si>
+    <t>Sair</t>
+  </si>
+  <si>
+    <t>Thoát</t>
+  </si>
+  <si>
+    <t>RemoteIP</t>
+  </si>
+  <si>
+    <t>遠端位址</t>
+  </si>
+  <si>
+    <t>Remote Address</t>
+  </si>
+  <si>
+    <t>リモートアドレス</t>
+  </si>
+  <si>
+    <t>Remote-Adresse</t>
+  </si>
+  <si>
+    <t>Adresse distante</t>
+  </si>
+  <si>
+    <t>Dirección remota</t>
+  </si>
+  <si>
+    <t>Endereço remoto</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>儲存</t>
+  </si>
+  <si>
+    <t>保存</t>
+  </si>
+  <si>
+    <t>Speichern</t>
+  </si>
+  <si>
+    <t>Enregistrer</t>
+  </si>
+  <si>
+    <t>Guardar</t>
+  </si>
+  <si>
+    <t>Salvar</t>
+  </si>
+  <si>
+    <t>Cancel</t>
+  </si>
+  <si>
+    <t>取消</t>
+  </si>
+  <si>
+    <t>キャンセル</t>
+  </si>
+  <si>
+    <t>Abbrechen</t>
+  </si>
+  <si>
+    <t>Annuler</t>
+  </si>
+  <si>
+    <t>Cancelar</t>
+  </si>
+  <si>
+    <t>Hủy</t>
+  </si>
+  <si>
+    <t>EnterName</t>
+  </si>
+  <si>
+    <t>輸入名稱</t>
+  </si>
+  <si>
+    <t>Enter Name</t>
+  </si>
+  <si>
+    <t>名前を入力</t>
+  </si>
+  <si>
+    <t>Name eingeben</t>
+  </si>
+  <si>
+    <t>Entrer le nom</t>
+  </si>
+  <si>
+    <t>Ingrese nombre</t>
+  </si>
+  <si>
+    <t>Digite o nome</t>
+  </si>
+  <si>
+    <t>Nhập tên</t>
+  </si>
+  <si>
+    <t>EnterIp</t>
+  </si>
+  <si>
+    <t>輸入位址</t>
+  </si>
+  <si>
+    <t>Enter Address</t>
+  </si>
+  <si>
+    <t>アドレスを入力</t>
+  </si>
+  <si>
+    <t>Adresse eingeben</t>
+  </si>
+  <si>
+    <t>Entrer l'adresse</t>
+  </si>
+  <si>
+    <t>Ingrese dirección</t>
+  </si>
+  <si>
+    <t>Digite o endereço</t>
+  </si>
+  <si>
+    <t>EnterRemotePort</t>
+  </si>
+  <si>
+    <t>輸入遠端端口</t>
+  </si>
+  <si>
+    <t>Enter Remote Port</t>
+  </si>
+  <si>
+    <t>リモートポートを入力</t>
+  </si>
+  <si>
+    <t>Remote-Port eingeben</t>
+  </si>
+  <si>
+    <t>Entrer le port distant</t>
+  </si>
+  <si>
+    <t>Ingrese puerto remoto</t>
+  </si>
+  <si>
+    <t>Digite a porta remota</t>
+  </si>
+  <si>
+    <t>Nhập cổng từ xa</t>
+  </si>
+  <si>
+    <t>EnterLocalPort</t>
+  </si>
+  <si>
+    <t>輸入本地端口</t>
+  </si>
+  <si>
+    <t>Enter Local Port</t>
+  </si>
+  <si>
+    <t>ローカルポートを入力</t>
+  </si>
+  <si>
+    <t>Lokalen Port eingeben</t>
+  </si>
+  <si>
+    <t>Entrer le port local</t>
+  </si>
+  <si>
+    <t>Ingrese puerto local</t>
+  </si>
+  <si>
+    <t>Digite a porta local</t>
+  </si>
+  <si>
+    <t>Nhập cổng cục bộ</t>
+  </si>
+  <si>
+    <t>Connecting</t>
+  </si>
+  <si>
+    <t>連接中</t>
+  </si>
+  <si>
+    <t>接続中</t>
+  </si>
+  <si>
+    <t>Verbinden</t>
+  </si>
+  <si>
+    <t>Connexion en cours</t>
+  </si>
+  <si>
+    <t>Conectando</t>
+  </si>
+  <si>
+    <t>NotConnecting</t>
+  </si>
+  <si>
+    <t>未連接</t>
+  </si>
+  <si>
+    <t>Not Connected</t>
+  </si>
+  <si>
+    <t>未接続</t>
+  </si>
+  <si>
+    <t>Nicht verbunden</t>
+  </si>
+  <si>
+    <t>Non connecté</t>
+  </si>
+  <si>
+    <t>No conectado</t>
+  </si>
+  <si>
+    <t>Não conectado</t>
+  </si>
+  <si>
+    <t>OriginalData</t>
+  </si>
+  <si>
+    <t>原始資料</t>
+  </si>
+  <si>
+    <t>Original Data</t>
+  </si>
+  <si>
+    <t>元データ</t>
+  </si>
+  <si>
+    <t>Originaldaten</t>
+  </si>
+  <si>
+    <t>Données originales</t>
+  </si>
+  <si>
+    <t>Datos originales</t>
+  </si>
+  <si>
+    <t>Dados originais</t>
+  </si>
+  <si>
+    <t>Dữ liệu gốc</t>
+  </si>
+  <si>
+    <t>Robot10</t>
+  </si>
+  <si>
+    <t>機器人-十進制</t>
+  </si>
+  <si>
+    <t>Robot-Decimal</t>
+  </si>
+  <si>
+    <t>ロボット-10進数</t>
+  </si>
+  <si>
+    <t>Roboter-Dezimal</t>
+  </si>
+  <si>
+    <t>Robot-Décimal</t>
+  </si>
+  <si>
+    <t>Robô-Decimal</t>
+  </si>
+  <si>
+    <t>Robot-Thập phân</t>
+  </si>
+  <si>
+    <t>Robot16</t>
+  </si>
+  <si>
+    <t>機器人-十六進制</t>
+  </si>
+  <si>
+    <t>Robot-Hexadecimal</t>
+  </si>
+  <si>
+    <t>ロボット-16進数</t>
+  </si>
+  <si>
+    <t>Roboter-Hexadezimal</t>
+  </si>
+  <si>
+    <t>Robot-Hexadécimal</t>
+  </si>
+  <si>
+    <t>Robô-Hexadecimal</t>
+  </si>
+  <si>
+    <t>Robot-Thập lục phân</t>
   </si>
   <si>
     <t xml:space="preserve">No image input yet
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>en-US,English</t>
-  </si>
-  <si>
-    <t>名稱</t>
-  </si>
-  <si>
-    <t>網絡協議</t>
-  </si>
-  <si>
-    <t>Remote Port</t>
-  </si>
-  <si>
-    <t>遠端端口</t>
-  </si>
-  <si>
-    <t>Local Port</t>
-  </si>
-  <si>
-    <t>本地端口</t>
-  </si>
-  <si>
-    <t>轉發目標</t>
-  </si>
-  <si>
-    <t>網絡狀態</t>
-  </si>
-  <si>
-    <t>Mask</t>
-  </si>
-  <si>
-    <t>NetProtocol</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LocalPort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NetState</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ForwardTarget</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RemotePort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Protocol</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>退出</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remote IP</t>
-  </si>
-  <si>
-    <t>RemoteIP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遠端位址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Save</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>儲存</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>取消</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cancel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterIp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterRemotePort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EnterLocalPort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入位址</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入遠端端口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>輸入本地端口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enter Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enter IP address</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enter Remote Port</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enter Local Port</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Connecting</t>
-  </si>
-  <si>
-    <t>Connecting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>連接中</t>
-  </si>
-  <si>
-    <t>NotConnecting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未連接</t>
-  </si>
-  <si>
-    <t>Not Connecting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遮罩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>State</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Target</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>original data</t>
-  </si>
-  <si>
-    <t>OriginalData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>原始資料</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Robot 10</t>
-  </si>
-  <si>
-    <t>機器人-十進制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Robot 16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>機器人-十六進制</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Robot10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Robot16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ịa chỉ từ xa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>u</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nhập </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ịa chỉ</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Đ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>ang kết nối</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ch</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ư</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>a kết nối</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -281,6 +698,19 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -308,7 +738,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -331,12 +761,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -377,14 +833,266 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
-    <cellStyle name="一般 2" xfId="1"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <name val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -395,6 +1103,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4CC7E177-8CDD-4069-9B2E-DA401015B088}" name="表格2" displayName="表格2" ref="A1:I21" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:I21" xr:uid="{4CC7E177-8CDD-4069-9B2E-DA401015B088}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{3858EF9F-3E82-4A91-AA55-2B89542A4FB5}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{CFE36AFA-E677-4759-921C-C3B2C5351BE1}" name="zh-TW,繁體中文" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{0E5C5B2A-DA75-40A1-8B4E-757FA3B871DB}" name="en-US,English" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{5D8A9AFE-884C-47BE-911B-2FA91FABDF9D}" name="ja-JP,日本語" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FC61F46D-674B-4930-8C49-A6C724B357DD}" name="de-DE,Deutsch" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{F741016E-F673-41AB-8CC2-01DA05DAC343}" name="fr-FR,Français" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{080C22DC-200F-48A0-865C-83E1DB5C08CC}" name="es-ES,Español" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{68CEAE7A-2341-4FE9-95B1-A214142B9C4C}" name="pt-BR,Português" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{99B1B462-CD19-456C-A7DD-239A1CABFA2F}" name="vi-VN,Tiếng Việt" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -594,17 +1320,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W364"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U364"/>
+  <sheetFormatPr defaultColWidth="14.3984375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="53.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="111.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="14.42578125" style="6"/>
+    <col min="1" max="1" width="22.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="25.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.8984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.8984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="14.3984375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -612,240 +1343,645 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="17"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="17"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="15" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="17"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="17"/>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="17"/>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J8" s="17"/>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>124</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="J18" s="17"/>
+    </row>
+    <row r="19" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20" s="17"/>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="7"/>
-    </row>
-    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="I21" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="18"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4"/>
       <c r="B23" s="2"/>
       <c r="C23" s="7"/>
     </row>
-    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4"/>
       <c r="B24" s="2"/>
       <c r="C24" s="7"/>
@@ -867,10 +2003,8 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4"/>
       <c r="B25" s="2"/>
       <c r="C25" s="7"/>
@@ -892,1377 +2026,1378 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
       <c r="C26" s="7"/>
     </row>
-    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="1"/>
       <c r="C27" s="7"/>
     </row>
-    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="7"/>
     </row>
-    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="7"/>
     </row>
-    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="7"/>
     </row>
-    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
       <c r="B31" s="1"/>
       <c r="C31" s="7"/>
     </row>
-    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3"/>
       <c r="B32" s="1"/>
       <c r="C32" s="7"/>
     </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3"/>
       <c r="B33" s="1"/>
       <c r="C33" s="7"/>
     </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3"/>
       <c r="B34" s="1"/>
       <c r="C34" s="7"/>
     </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="1"/>
       <c r="C35" s="7"/>
     </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3"/>
       <c r="B36" s="1"/>
       <c r="C36" s="7"/>
     </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
       <c r="B37" s="1"/>
       <c r="C37" s="7"/>
     </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
       <c r="B38" s="1"/>
       <c r="C38" s="7"/>
     </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
       <c r="B39" s="1"/>
       <c r="C39" s="7"/>
     </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="7"/>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="1"/>
       <c r="C41" s="7"/>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="1"/>
       <c r="C42" s="7"/>
     </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="1"/>
       <c r="C43" s="7"/>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3"/>
       <c r="B44" s="1"/>
       <c r="C44" s="7"/>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="1"/>
       <c r="C45" s="7"/>
     </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="1"/>
       <c r="C46" s="7"/>
     </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="1"/>
       <c r="C47" s="7"/>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="1"/>
       <c r="C48" s="7"/>
     </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3"/>
       <c r="B49" s="1"/>
       <c r="C49" s="7"/>
     </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="1"/>
       <c r="C50" s="7"/>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="1"/>
       <c r="C51" s="7"/>
     </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="1"/>
       <c r="C52" s="7"/>
     </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="1"/>
       <c r="C53" s="7"/>
     </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3"/>
       <c r="B54" s="1"/>
       <c r="C54" s="7"/>
     </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3"/>
       <c r="B55" s="1"/>
       <c r="C55" s="7"/>
     </row>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3"/>
       <c r="B56" s="1"/>
       <c r="C56" s="7"/>
     </row>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3"/>
       <c r="B57" s="1"/>
       <c r="C57" s="7"/>
     </row>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3"/>
       <c r="B58" s="1"/>
       <c r="C58" s="7"/>
     </row>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3"/>
       <c r="B59" s="1"/>
       <c r="C59" s="7"/>
     </row>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3"/>
       <c r="B60" s="1"/>
       <c r="C60" s="7"/>
     </row>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3"/>
       <c r="B61" s="1"/>
       <c r="C61" s="7"/>
     </row>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3"/>
       <c r="B62" s="1"/>
       <c r="C62" s="7"/>
     </row>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3"/>
       <c r="B63" s="1"/>
       <c r="C63" s="7"/>
     </row>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3"/>
       <c r="B64" s="1"/>
       <c r="C64" s="7"/>
     </row>
-    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3"/>
       <c r="B65" s="1"/>
       <c r="C65" s="7"/>
     </row>
-    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3"/>
       <c r="B66" s="1"/>
       <c r="C66" s="7"/>
     </row>
-    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3"/>
       <c r="B67" s="1"/>
       <c r="C67" s="7"/>
     </row>
-    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="1"/>
       <c r="C68" s="7"/>
     </row>
-    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="1"/>
       <c r="C69" s="7"/>
     </row>
-    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="1"/>
       <c r="C70" s="7"/>
     </row>
-    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="1"/>
       <c r="C71" s="7"/>
     </row>
-    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="1"/>
       <c r="C72" s="7"/>
     </row>
-    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="1"/>
       <c r="C73" s="7"/>
     </row>
-    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="1"/>
       <c r="C74" s="7"/>
     </row>
-    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3"/>
       <c r="B75" s="1"/>
       <c r="C75" s="7"/>
     </row>
-    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="1"/>
       <c r="C76" s="7"/>
     </row>
-    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="1"/>
       <c r="C77" s="7"/>
     </row>
-    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="1"/>
       <c r="C78" s="7"/>
     </row>
-    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
     </row>
-    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="1"/>
     </row>
-    <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="C81" s="1"/>
     </row>
-    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="1"/>
     </row>
-    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="1"/>
       <c r="C83" s="7"/>
     </row>
-    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3"/>
       <c r="B84" s="1"/>
     </row>
-    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3"/>
       <c r="B85" s="1"/>
       <c r="C85" s="7"/>
     </row>
-    <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3"/>
       <c r="B86" s="1"/>
       <c r="C86" s="7"/>
     </row>
-    <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4"/>
       <c r="B87" s="2"/>
       <c r="C87" s="7"/>
     </row>
-    <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="2"/>
       <c r="C88" s="7"/>
     </row>
-    <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="2"/>
       <c r="C89" s="7"/>
     </row>
-    <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="2"/>
       <c r="C90" s="7"/>
     </row>
-    <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="2"/>
       <c r="C91" s="7"/>
     </row>
-    <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="2"/>
       <c r="C92" s="7"/>
     </row>
-    <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="2"/>
       <c r="C93" s="7"/>
     </row>
-    <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="2"/>
       <c r="C94" s="7"/>
     </row>
-    <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="2"/>
       <c r="C95" s="7"/>
     </row>
-    <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="3"/>
       <c r="B96" s="1"/>
       <c r="C96" s="7"/>
     </row>
-    <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3"/>
       <c r="B97" s="1"/>
       <c r="C97" s="7"/>
     </row>
-    <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="1"/>
       <c r="C98" s="7"/>
     </row>
-    <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="1"/>
       <c r="C99" s="7"/>
     </row>
-    <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="1"/>
       <c r="C100" s="7"/>
     </row>
-    <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="1"/>
       <c r="C101" s="7"/>
     </row>
-    <row r="102" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="138" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="1"/>
       <c r="C102" s="7"/>
     </row>
-    <row r="103" spans="1:3" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3"/>
       <c r="B103" s="1"/>
       <c r="C103" s="7"/>
     </row>
-    <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="1"/>
       <c r="C104" s="7"/>
     </row>
-    <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="1"/>
       <c r="C105" s="7"/>
     </row>
-    <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="1"/>
       <c r="C106" s="7"/>
     </row>
-    <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3"/>
       <c r="B107" s="1"/>
       <c r="C107" s="7"/>
     </row>
-    <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="1"/>
       <c r="C108" s="7"/>
     </row>
-    <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="1"/>
       <c r="C109" s="7"/>
     </row>
-    <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="1"/>
       <c r="C110" s="7"/>
     </row>
-    <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="1"/>
       <c r="C111" s="7"/>
     </row>
-    <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="1"/>
       <c r="C112" s="7"/>
     </row>
-    <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3"/>
       <c r="B113" s="1"/>
       <c r="C113" s="7"/>
     </row>
-    <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3"/>
       <c r="B114" s="1"/>
       <c r="C114" s="7"/>
     </row>
-    <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="1"/>
       <c r="C115" s="7"/>
     </row>
-    <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="1"/>
       <c r="C116" s="7"/>
     </row>
-    <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="1"/>
       <c r="C117" s="7"/>
     </row>
-    <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3"/>
       <c r="B118" s="1"/>
       <c r="C118" s="7"/>
     </row>
-    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3"/>
       <c r="B119" s="1"/>
       <c r="C119" s="7"/>
     </row>
-    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="1"/>
       <c r="C120" s="7"/>
     </row>
-    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3"/>
       <c r="B121" s="1"/>
       <c r="C121" s="7"/>
     </row>
-    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3"/>
       <c r="B122" s="1"/>
       <c r="C122" s="7"/>
     </row>
-    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3"/>
       <c r="B123" s="1"/>
       <c r="C123" s="7"/>
     </row>
-    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3"/>
       <c r="B124" s="1"/>
       <c r="C124" s="7"/>
     </row>
-    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3"/>
       <c r="B125" s="1"/>
       <c r="C125" s="7"/>
     </row>
-    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3"/>
     </row>
-    <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
     </row>
-    <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
     </row>
-    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
     </row>
-    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
     </row>
-    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3"/>
     </row>
-    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3"/>
     </row>
-    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3"/>
     </row>
-    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3"/>
     </row>
-    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3"/>
     </row>
-    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
     </row>
-    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
     </row>
-    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
     </row>
-    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
     </row>
-    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
     </row>
-    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5"/>
       <c r="B141" s="7"/>
       <c r="C141" s="7"/>
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5"/>
       <c r="B142" s="7"/>
       <c r="C142" s="7"/>
     </row>
-    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5"/>
       <c r="B143" s="7"/>
       <c r="C143" s="7"/>
     </row>
-    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5"/>
       <c r="B144" s="7"/>
       <c r="C144" s="7"/>
     </row>
-    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5"/>
       <c r="B145" s="7"/>
       <c r="C145" s="7"/>
     </row>
-    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5"/>
       <c r="B146" s="7"/>
       <c r="C146" s="7"/>
     </row>
-    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5"/>
       <c r="B147" s="7"/>
       <c r="C147" s="7"/>
     </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="5"/>
       <c r="B148" s="7"/>
       <c r="C148" s="7"/>
     </row>
-    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5"/>
       <c r="B149" s="7"/>
       <c r="C149" s="7"/>
     </row>
-    <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5"/>
       <c r="B150" s="7"/>
       <c r="C150" s="7"/>
     </row>
-    <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5"/>
       <c r="B151" s="7"/>
       <c r="C151" s="7"/>
     </row>
-    <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5"/>
       <c r="B152" s="7"/>
       <c r="C152" s="7"/>
     </row>
-    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5"/>
       <c r="B153" s="7"/>
       <c r="C153" s="7"/>
     </row>
-    <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5"/>
       <c r="B154" s="7"/>
       <c r="C154" s="7"/>
     </row>
-    <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5"/>
       <c r="B155" s="7"/>
       <c r="C155" s="7"/>
     </row>
-    <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5"/>
       <c r="B156" s="7"/>
       <c r="C156" s="7"/>
     </row>
-    <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5"/>
       <c r="B157" s="7"/>
       <c r="C157" s="7"/>
     </row>
-    <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5"/>
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
     </row>
-    <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5"/>
       <c r="B159" s="7"/>
       <c r="C159" s="7"/>
     </row>
-    <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5"/>
       <c r="B160" s="7"/>
       <c r="C160" s="7"/>
     </row>
-    <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5"/>
       <c r="B161" s="7"/>
       <c r="C161" s="7"/>
     </row>
-    <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5"/>
       <c r="B162" s="7"/>
       <c r="C162" s="7"/>
     </row>
-    <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5"/>
       <c r="B163" s="7"/>
       <c r="C163" s="7"/>
     </row>
-    <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5"/>
       <c r="B164" s="7"/>
       <c r="C164" s="7"/>
     </row>
-    <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5"/>
       <c r="B165" s="7"/>
       <c r="C165" s="7"/>
     </row>
-    <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5"/>
       <c r="B166" s="7"/>
       <c r="C166" s="7"/>
     </row>
-    <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5"/>
       <c r="B167" s="7"/>
       <c r="C167" s="7"/>
     </row>
-    <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5"/>
       <c r="B168" s="7"/>
       <c r="C168" s="7"/>
     </row>
-    <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5"/>
       <c r="B169" s="7"/>
       <c r="C169" s="7"/>
     </row>
-    <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5"/>
       <c r="B170" s="7"/>
       <c r="C170" s="7"/>
     </row>
-    <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5"/>
       <c r="B171" s="7"/>
     </row>
-    <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5"/>
       <c r="B172" s="7"/>
     </row>
-    <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5"/>
       <c r="B173" s="7"/>
     </row>
-    <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5"/>
       <c r="B174" s="7"/>
     </row>
-    <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5"/>
       <c r="B175" s="7"/>
     </row>
-    <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="5"/>
       <c r="B176" s="7"/>
     </row>
-    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5"/>
       <c r="B177" s="7"/>
     </row>
-    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="5"/>
       <c r="B178" s="7"/>
     </row>
-    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="5"/>
       <c r="B179" s="7"/>
     </row>
-    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="5"/>
       <c r="B180" s="7"/>
     </row>
-    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5"/>
       <c r="B181" s="7"/>
     </row>
-    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="5"/>
       <c r="B182" s="7"/>
     </row>
-    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="5"/>
       <c r="B183" s="7"/>
     </row>
-    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="5"/>
       <c r="B184" s="7"/>
     </row>
-    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="5"/>
       <c r="B185" s="7"/>
     </row>
-    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="5"/>
       <c r="B186" s="7"/>
     </row>
-    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="5"/>
       <c r="B187" s="7"/>
     </row>
-    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="5"/>
       <c r="B188" s="7"/>
     </row>
-    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5"/>
       <c r="B189" s="7"/>
     </row>
-    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5"/>
       <c r="B190" s="7"/>
       <c r="C190" s="8"/>
     </row>
-    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5"/>
       <c r="B191" s="7"/>
     </row>
-    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="5"/>
       <c r="B192" s="7"/>
     </row>
-    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="5"/>
       <c r="B193" s="7"/>
     </row>
-    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="5"/>
       <c r="B194" s="7"/>
       <c r="C194" s="7"/>
     </row>
-    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="5"/>
       <c r="B195" s="7"/>
       <c r="C195" s="7"/>
     </row>
-    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="5"/>
       <c r="B196" s="7"/>
     </row>
-    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="5"/>
       <c r="B197" s="7"/>
     </row>
-    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="5"/>
       <c r="B198" s="7"/>
     </row>
-    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="3"/>
       <c r="B199" s="1"/>
       <c r="C199" s="9"/>
     </row>
-    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="3"/>
       <c r="B200" s="1"/>
       <c r="C200" s="9"/>
     </row>
-    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="3"/>
       <c r="B201" s="1"/>
       <c r="C201" s="9"/>
     </row>
-    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="3"/>
       <c r="B202" s="1"/>
       <c r="C202" s="9"/>
     </row>
-    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3"/>
       <c r="B203" s="1"/>
       <c r="C203" s="9"/>
     </row>
-    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="3"/>
       <c r="B204" s="1"/>
       <c r="C204" s="7"/>
     </row>
-    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="3"/>
       <c r="B205" s="1"/>
       <c r="C205" s="7"/>
     </row>
-    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="3"/>
       <c r="B206" s="1"/>
       <c r="C206" s="7"/>
     </row>
-    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="3"/>
       <c r="B207" s="1"/>
       <c r="C207" s="7"/>
     </row>
-    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="3"/>
       <c r="B208" s="1"/>
       <c r="C208" s="7"/>
     </row>
-    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3"/>
       <c r="B209" s="1"/>
       <c r="C209" s="7"/>
     </row>
-    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3"/>
       <c r="B210" s="1"/>
       <c r="C210" s="7"/>
     </row>
-    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="3"/>
       <c r="B211" s="1"/>
       <c r="C211" s="7"/>
     </row>
-    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="3"/>
       <c r="B212" s="1"/>
       <c r="C212" s="7"/>
     </row>
-    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="3"/>
       <c r="B213" s="1"/>
       <c r="C213" s="7"/>
     </row>
-    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="3"/>
       <c r="B214" s="1"/>
       <c r="C214" s="7"/>
     </row>
-    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3"/>
       <c r="B215" s="1"/>
       <c r="C215" s="7"/>
     </row>
-    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3"/>
       <c r="B216" s="1"/>
       <c r="C216" s="7"/>
     </row>
-    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3"/>
       <c r="B217" s="1"/>
       <c r="C217" s="7"/>
     </row>
-    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="3"/>
       <c r="B218" s="1"/>
       <c r="C218" s="7"/>
     </row>
-    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="3"/>
       <c r="B219" s="1"/>
       <c r="C219" s="7"/>
     </row>
-    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="3"/>
       <c r="B220" s="1"/>
       <c r="C220" s="7"/>
     </row>
-    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="3"/>
       <c r="B221" s="1"/>
       <c r="C221" s="7"/>
     </row>
-    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="3"/>
       <c r="B222" s="1"/>
       <c r="C222" s="7"/>
     </row>
-    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="3"/>
       <c r="B223" s="1"/>
       <c r="C223" s="7"/>
     </row>
-    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="3"/>
       <c r="B224" s="1"/>
       <c r="C224" s="7"/>
     </row>
-    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3"/>
       <c r="B225" s="1"/>
       <c r="C225" s="7"/>
     </row>
-    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3"/>
       <c r="B226" s="1"/>
       <c r="C226" s="7"/>
     </row>
-    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3"/>
       <c r="B227" s="1"/>
       <c r="C227" s="7"/>
     </row>
-    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="3"/>
       <c r="B228" s="1"/>
       <c r="C228" s="7"/>
     </row>
-    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="3"/>
       <c r="B229" s="1"/>
       <c r="C229" s="7"/>
     </row>
-    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="3"/>
       <c r="B230" s="1"/>
       <c r="C230" s="7"/>
     </row>
-    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="3"/>
       <c r="B231" s="1"/>
       <c r="C231" s="7"/>
     </row>
-    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="3"/>
       <c r="B232" s="1"/>
       <c r="C232" s="7"/>
     </row>
-    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3"/>
       <c r="B233" s="1"/>
       <c r="C233" s="7"/>
     </row>
-    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="3"/>
       <c r="B234" s="1"/>
       <c r="C234" s="7"/>
     </row>
-    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="3"/>
       <c r="B235" s="1"/>
       <c r="C235" s="7"/>
     </row>
-    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="3"/>
       <c r="B236" s="1"/>
       <c r="C236" s="7"/>
     </row>
-    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3"/>
       <c r="B237" s="1"/>
       <c r="C237" s="7"/>
     </row>
-    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="3"/>
       <c r="B238" s="1"/>
       <c r="C238" s="7"/>
     </row>
-    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="3"/>
       <c r="B239" s="1"/>
       <c r="C239" s="7"/>
     </row>
-    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3"/>
       <c r="B240" s="1"/>
       <c r="C240" s="7"/>
     </row>
-    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="3"/>
       <c r="B241" s="1"/>
       <c r="C241" s="7"/>
     </row>
-    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="3"/>
       <c r="B242" s="1"/>
       <c r="C242" s="7"/>
     </row>
-    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3"/>
       <c r="B243" s="1"/>
       <c r="C243" s="7"/>
     </row>
-    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3"/>
       <c r="B244" s="1"/>
       <c r="C244" s="7"/>
     </row>
-    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3"/>
       <c r="B245" s="1"/>
       <c r="C245" s="7"/>
     </row>
-    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3"/>
       <c r="B246" s="1"/>
       <c r="C246" s="7"/>
     </row>
-    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3"/>
       <c r="B247" s="1"/>
       <c r="C247" s="7"/>
     </row>
-    <row r="248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="3"/>
       <c r="B248" s="1"/>
       <c r="C248" s="7"/>
     </row>
-    <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="3"/>
       <c r="B249" s="1"/>
       <c r="C249" s="7"/>
     </row>
-    <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A250" s="3"/>
       <c r="B250" s="1"/>
       <c r="C250" s="7"/>
     </row>
-    <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="3"/>
       <c r="B251" s="1"/>
       <c r="C251" s="7"/>
     </row>
-    <row r="252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="3"/>
       <c r="B252" s="1"/>
       <c r="C252" s="7"/>
     </row>
-    <row r="253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" s="3"/>
       <c r="B253" s="1"/>
     </row>
-    <row r="254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A254" s="3"/>
       <c r="B254" s="1"/>
     </row>
-    <row r="255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A255" s="3"/>
       <c r="B255" s="1"/>
       <c r="C255" s="7"/>
     </row>
-    <row r="256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A256" s="3"/>
       <c r="B256" s="1"/>
       <c r="C256" s="7"/>
     </row>
-    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A257" s="3"/>
       <c r="B257" s="1"/>
       <c r="C257" s="7"/>
     </row>
-    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A258" s="3"/>
       <c r="B258" s="1"/>
       <c r="C258" s="7"/>
     </row>
-    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A259" s="3"/>
       <c r="B259" s="1"/>
       <c r="C259" s="7"/>
     </row>
-    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3"/>
       <c r="B260" s="1"/>
       <c r="C260" s="7"/>
     </row>
-    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3"/>
       <c r="B261" s="1"/>
       <c r="C261" s="7"/>
     </row>
-    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3"/>
       <c r="B262" s="1"/>
       <c r="C262" s="7"/>
     </row>
-    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="3"/>
       <c r="B263" s="1"/>
       <c r="C263" s="7"/>
     </row>
-    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="3"/>
       <c r="B264" s="1"/>
       <c r="C264" s="7"/>
     </row>
-    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A265" s="3"/>
       <c r="B265" s="1"/>
       <c r="C265" s="7"/>
     </row>
-    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A266" s="3"/>
       <c r="B266" s="1"/>
       <c r="C266" s="7"/>
     </row>
-    <row r="267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A267" s="3"/>
       <c r="B267" s="1"/>
     </row>
-    <row r="268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A268" s="3"/>
       <c r="B268" s="1"/>
     </row>
-    <row r="269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3"/>
       <c r="B269" s="1"/>
     </row>
-    <row r="270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A270" s="3"/>
       <c r="B270" s="1"/>
     </row>
-    <row r="271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3"/>
       <c r="B271" s="1"/>
     </row>
-    <row r="272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3"/>
       <c r="B272" s="1"/>
     </row>
-    <row r="273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A273" s="3"/>
       <c r="B273" s="1"/>
       <c r="C273" s="10"/>
     </row>
-    <row r="274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3"/>
       <c r="B274" s="1"/>
       <c r="C274" s="10"/>
     </row>
-    <row r="275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" s="3"/>
       <c r="B275" s="1"/>
       <c r="C275" s="10"/>
     </row>
-    <row r="276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A276" s="5"/>
       <c r="B276" s="1"/>
       <c r="C276" s="10"/>
     </row>
-    <row r="277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A277" s="5"/>
       <c r="B277" s="1"/>
       <c r="C277" s="10"/>
     </row>
-    <row r="278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A278" s="5"/>
       <c r="B278" s="1"/>
       <c r="C278" s="10"/>
     </row>
-    <row r="279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A279" s="5"/>
       <c r="B279" s="1"/>
       <c r="C279" s="10"/>
     </row>
-    <row r="280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="5"/>
       <c r="B280" s="1"/>
       <c r="C280" s="10"/>
     </row>
-    <row r="281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A281" s="5"/>
       <c r="B281" s="1"/>
       <c r="C281" s="10"/>
     </row>
-    <row r="282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A282" s="5"/>
       <c r="B282" s="1"/>
       <c r="C282" s="10"/>
     </row>
-    <row r="283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A283" s="5"/>
       <c r="B283" s="1"/>
       <c r="C283" s="10"/>
     </row>
-    <row r="284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="5"/>
       <c r="B284" s="1"/>
       <c r="C284" s="10"/>
     </row>
-    <row r="285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="5"/>
       <c r="B285" s="1"/>
       <c r="C285" s="10"/>
     </row>
-    <row r="286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A286" s="5"/>
       <c r="B286" s="1"/>
       <c r="C286" s="10"/>
     </row>
-    <row r="287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A287" s="5"/>
       <c r="B287" s="1"/>
       <c r="C287" s="10"/>
     </row>
-    <row r="288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="5"/>
       <c r="B288" s="1"/>
       <c r="C288" s="10"/>
     </row>
-    <row r="289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="5"/>
       <c r="B289" s="1"/>
       <c r="C289" s="10"/>
     </row>
-    <row r="290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="5"/>
       <c r="B290" s="1"/>
       <c r="C290" s="10"/>
     </row>
-    <row r="291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A291" s="5"/>
       <c r="C291" s="10"/>
     </row>
-    <row r="292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A292" s="5"/>
       <c r="C292" s="10"/>
     </row>
-    <row r="293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A293" s="5"/>
       <c r="B293" s="1"/>
       <c r="C293" s="10"/>
     </row>
-    <row r="294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="5"/>
       <c r="B294" s="1"/>
       <c r="C294" s="10"/>
     </row>
-    <row r="295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="5"/>
       <c r="B295" s="1"/>
       <c r="C295" s="10"/>
     </row>
-    <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="5"/>
       <c r="B296" s="1"/>
       <c r="C296" s="10"/>
     </row>
-    <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="5"/>
       <c r="B297" s="1"/>
     </row>
-    <row r="298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="5"/>
       <c r="B298" s="1"/>
     </row>
-    <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="5"/>
       <c r="B299" s="1"/>
     </row>
-    <row r="300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A300" s="5"/>
       <c r="B300" s="1"/>
     </row>
-    <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A301" s="5"/>
       <c r="B301" s="1"/>
     </row>
-    <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A302" s="5"/>
       <c r="B302" s="1"/>
     </row>
-    <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A303" s="5"/>
       <c r="B303" s="1"/>
     </row>
-    <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="5"/>
       <c r="B304" s="1"/>
     </row>
-    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A305" s="5"/>
     </row>
-    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A306" s="5"/>
       <c r="B306" s="1"/>
     </row>
-    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="5"/>
       <c r="B307" s="1"/>
     </row>
-    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A308" s="5"/>
       <c r="B308" s="1"/>
     </row>
-    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A309" s="5"/>
       <c r="B309" s="1"/>
     </row>
-    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A310" s="5"/>
       <c r="B310" s="1"/>
     </row>
-    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A311" s="5"/>
       <c r="B311" s="1"/>
     </row>
-    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A312" s="5"/>
       <c r="B312" s="1"/>
     </row>
-    <row r="364" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="3:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C364" s="6" t="s">
-        <v>2</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>